--- a/V9_ExternalRemote/TOS_RTD_Bridge.xlsx
+++ b/V9_ExternalRemote/TOS_RTD_Bridge.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d02bc7633862b244/Desktop/WSGTA/Github/universal-or-strategy/V9_ExternalRemote/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohammed Khalid\OneDrive\Desktop\WSGTA\Github\universal-or-strategy\V9_ExternalRemote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_2B59D2BFD3F0575EAEFEC353531510344D078D03" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36BC8310-802B-46D6-BD5C-6CAF9DDC4C37}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BEEBF4C-5E19-4F84-95FE-922F40A7FE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7430" yWindow="3790" windowWidth="6460" windowHeight="6860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,13 +43,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="6"/>
@@ -78,9 +84,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -106,32 +113,39 @@
         <v>N/A</v>
         <stp/>
         <stp>LAST</stp>
+        <stp>/MES[H26]</stp>
+        <tr r="A7" s="1"/>
+      </tp>
+      <tp t="s">
+        <v>N/A</v>
+        <stp/>
+        <stp>LAST</stp>
         <stp>/MES</stp>
         <tr r="A5" s="1"/>
       </tp>
-      <tp>
-        <v>6940.76</v>
+      <tp t="s">
+        <v>loading</v>
         <stp/>
         <stp>CUSTOM4</stp>
         <stp>/MES:XCME</stp>
         <tr r="B1" s="1"/>
       </tp>
-      <tp>
-        <v>4950</v>
+      <tp t="s">
+        <v>loading</v>
         <stp/>
         <stp>CUSTOM6</stp>
         <stp>/MGC:XCEC</stp>
         <tr r="C2" s="1"/>
       </tp>
-      <tp>
-        <v>6941.08</v>
+      <tp t="s">
+        <v>loading</v>
         <stp/>
         <stp>CUSTOM6</stp>
         <stp>/MES:XCME</stp>
         <tr r="C1" s="1"/>
       </tp>
-      <tp>
-        <v>4954.2</v>
+      <tp t="s">
+        <v>loading</v>
         <stp/>
         <stp>CUSTOM4</stp>
         <stp>/MGC:XCEC</stp>
@@ -140,10 +154,6 @@
     </main>
   </volType>
 </volTypes>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -431,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -442,26 +452,26 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1">
+      <c r="B1" t="str">
         <f>RTD("tos.rtd",,"CUSTOM4","/MES:XCME")</f>
-        <v>6940.76</v>
-      </c>
-      <c r="C1">
+        <v>loading</v>
+      </c>
+      <c r="C1" t="str">
         <f>RTD("tos.rtd",,"CUSTOM6","/MES:XCME")</f>
-        <v>6941.08</v>
+        <v>loading</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="str">
         <f>RTD("tos.rtd",,"CUSTOM4","/MGC:XCEC")</f>
-        <v>4954.2</v>
-      </c>
-      <c r="C2">
+        <v>loading</v>
+      </c>
+      <c r="C2" t="str">
         <f>RTD("tos.rtd",,"CUSTOM6","/MGC:XCEC")</f>
-        <v>4950</v>
+        <v>loading</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -470,7 +480,14 @@
         <v>N/A</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="str">
+        <f>RTD("tos.rtd", , "LAST", "/MES[H26]")</f>
+        <v>N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>